--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B2" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B3" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B4" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B5" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B6" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B7" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B8" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B9" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B10" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B11" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B12" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B13" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B14" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B15" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B16" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B17" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B18" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
       </c>
       <c r="B19" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>רולי אזרחי - מרחוק להורדה</v>
       </c>
       <c r="B20" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>נרקיס בר-און - לו היית להורדה</v>
       </c>
       <c r="B21" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>משה דוויק - שיר תודה להורדה</v>
       </c>
       <c r="B22" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
       </c>
       <c r="B23" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
       </c>
       <c r="B24" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
       </c>
       <c r="B25" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>אלי וינר - ניצחתי להורדה</v>
       </c>
       <c r="B26" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
       </c>
       <c r="B27" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>זהבה - עדיין ילד להורדה</v>
       </c>
       <c r="B28" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>רותם גבאי - שדה חמניה להורדה</v>
       </c>
       <c r="B29" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
       </c>
       <c r="B30" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,21 +821,91 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C32" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C33" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C34" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C35" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B31" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C31" t="str">
+      <c r="B36" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C36" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D36" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B2" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B3" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B4" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B5" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B6" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B7" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B8" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B9" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B10" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B11" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B12" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B13" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B14" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B15" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B16" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B17" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B18" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B19" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B20" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B21" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B22" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
       </c>
       <c r="B23" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>רולי אזרחי - מרחוק להורדה</v>
       </c>
       <c r="B24" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>נרקיס בר-און - לו היית להורדה</v>
       </c>
       <c r="B25" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>משה דוויק - שיר תודה להורדה</v>
       </c>
       <c r="B26" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
       </c>
       <c r="B27" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
       </c>
       <c r="B28" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
       </c>
       <c r="B29" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>אלי וינר - ניצחתי להורדה</v>
       </c>
       <c r="B30" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
       </c>
       <c r="B31" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>זהבה - עדיין ילד להורדה</v>
       </c>
       <c r="B32" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>רותם גבאי - שדה חמניה להורדה</v>
       </c>
       <c r="B33" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
       </c>
       <c r="B34" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
       </c>
       <c r="B35" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,21 +891,77 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C36" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C37" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C38" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C39" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B36" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C36" t="str">
+      <c r="B40" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C40" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D40" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B3" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B4" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B5" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B6" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B7" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B8" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B9" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B10" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B11" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B12" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B13" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B14" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B15" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B16" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B17" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B18" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B19" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B20" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B21" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B22" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B23" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B24" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B25" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B26" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B27" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B28" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B29" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B30" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B31" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B32" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B33" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B34" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B35" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B36" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B37" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B38" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B39" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,21 +947,441 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C40" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C41" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C42" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>שייה - לפח להורדה</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C43" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>רותם כהן - לשרוף להורדה</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C44" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>קלימה - תודה בורא עולם להורדה</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C45" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>דוד ברג - אזמרה להורדה</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C46" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>אבירם פרחן - בגדו בי להורדה</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C47" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C48" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C49" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>ירין מסס - נדבר באהבה להורדה</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C50" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>חן ביטון - התקרבתי להורדה</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C51" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C52" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C53" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>רולי אזרחי - מרחוק להורדה</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C54" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>נרקיס בר-און - לו היית להורדה</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C55" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>משה דוויק - שיר תודה להורדה</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C56" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C57" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C58" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C59" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>אלי וינר - ניצחתי להורדה</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C60" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C61" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>זהבה - עדיין ילד להורדה</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C62" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>רותם גבאי - שדה חמניה להורדה</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C63" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C64" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C65" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C66" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C67" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C68" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C69" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B40" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C40" t="str">
+      <c r="B70" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C70" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D70" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D70"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D80"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,7 +421,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -435,7 +435,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -449,7 +449,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -463,7 +463,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -491,7 +491,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -505,7 +505,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B12" t="str">
         <v>0</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שייה - לפח</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B13" t="str">
         <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B14" t="str">
         <v>0</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B15" t="str">
         <v>0</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B16" t="str">
         <v>0</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B17" t="str">
         <v>0</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B18" t="str">
         <v>0</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>מני חן - תני סימן קטן לאהבה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B19" t="str">
         <v>0</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ירין מסס - נדבר באהבה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B20" t="str">
         <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>חן ביטון - התקרבתי</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B21" t="str">
         <v>0</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>החצר האחורית של ג'וני - הזקן</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B22" t="str">
         <v>0</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אליה נרקיס - שכחת את הכל</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B23" t="str">
         <v>0</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רולי אזרחי - מרחוק</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B24" t="str">
         <v>0</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>נרקיס בר-און - לו היית</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B25" t="str">
         <v>0</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>משה דוויק - שיר תודה</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B26" t="str">
         <v>0</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>משה גמל - עולה לי בדמעות</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B27" t="str">
         <v>0</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B28" t="str">
         <v>0</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>חביב חיים בן אריה - ותזרח</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B29" t="str">
         <v>0</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אלי וינר - ניצחתי</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B30" t="str">
         <v>0</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B31" t="str">
         <v>0</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B32" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B33" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B34" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B35" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B36" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B37" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B38" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B39" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B40" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-05</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B41" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-05</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B42" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-05</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B43" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-05</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B44" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-05</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B45" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-05</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B46" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-05</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B47" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-05</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B48" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-05</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B49" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-05</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B50" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-05</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B51" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-05</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B52" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-05</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B53" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-05</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B54" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-05</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B55" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-05</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B56" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-05</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B57" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-05</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B58" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-05</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B59" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-05</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B60" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-05</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B61" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-05</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B62" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-05</v>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
       </c>
       <c r="B63" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-05</v>
@@ -1283,13 +1283,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>רולי אזרחי - מרחוק להורדה</v>
       </c>
       <c r="B64" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-05</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>נרקיס בר-און - לו היית להורדה</v>
       </c>
       <c r="B65" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-05</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>משה דוויק - שיר תודה להורדה</v>
       </c>
       <c r="B66" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-05</v>
@@ -1325,13 +1325,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
       </c>
       <c r="B67" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-05</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
       </c>
       <c r="B68" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-05</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
       </c>
       <c r="B69" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-05</v>
@@ -1367,21 +1367,161 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>אלי וינר - ניצחתי להורדה</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C70" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C71" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>זהבה - עדיין ילד להורדה</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C72" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>רותם גבאי - שדה חמניה להורדה</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C73" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C74" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C75" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C76" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C77" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C78" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C79" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B70" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C70" t="str">
+      <c r="B80" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C80" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D80" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,10 +418,10 @@
         <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B2" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -432,10 +432,10 @@
         <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B3" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -446,10 +446,10 @@
         <v>מאור יפרח - אמא</v>
       </c>
       <c r="B4" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -460,10 +460,10 @@
         <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B5" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -474,10 +474,10 @@
         <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B6" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -488,10 +488,10 @@
         <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B7" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -502,10 +502,10 @@
         <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B8" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -516,10 +516,10 @@
         <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B9" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -530,10 +530,10 @@
         <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B10" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -544,10 +544,10 @@
         <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B11" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B12" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B13" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B14" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B15" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B16" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B17" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B18" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B19" t="str">
         <v>0</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B20" t="str">
         <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B21" t="str">
         <v>0</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B22" t="str">
         <v>0</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>שייה - לפח</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B23" t="str">
         <v>0</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B24" t="str">
         <v>0</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B25" t="str">
         <v>0</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B26" t="str">
         <v>0</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B27" t="str">
         <v>0</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B28" t="str">
         <v>0</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>מני חן - תני סימן קטן לאהבה</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B29" t="str">
         <v>0</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ירין מסס - נדבר באהבה</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B30" t="str">
         <v>0</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>חן ביטון - התקרבתי</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B31" t="str">
         <v>0</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>החצר האחורית של ג'וני - הזקן</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B32" t="str">
         <v>0</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>אליה נרקיס - שכחת את הכל</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B33" t="str">
         <v>0</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>רולי אזרחי - מרחוק</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B34" t="str">
         <v>0</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>נרקיס בר-און - לו היית</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B35" t="str">
         <v>0</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>משה דוויק - שיר תודה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B36" t="str">
         <v>0</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>משה גמל - עולה לי בדמעות</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B37" t="str">
         <v>0</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B38" t="str">
         <v>0</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>חביב חיים בן אריה - ותזרח</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B39" t="str">
         <v>0</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>אלי וינר - ניצחתי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B40" t="str">
         <v>0</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-05</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B41" t="str">
         <v>0</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-05</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B42" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-05</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B43" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-05</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B44" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-05</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B45" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-05</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B46" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-05</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B47" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-05</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B48" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-05</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B49" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-05</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B50" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-05</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B51" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-05</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B52" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-05</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B53" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-05</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B54" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-05</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B55" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-05</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B56" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-05</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B57" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-05</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B58" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-05</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B59" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-05</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B60" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-05</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B61" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-05</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B62" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-05</v>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B63" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-05</v>
@@ -1283,13 +1283,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B64" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-05</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B65" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-05</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B66" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-05</v>
@@ -1325,13 +1325,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B67" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-05</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B68" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-05</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B69" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-05</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B70" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-05</v>
@@ -1381,13 +1381,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B71" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-05</v>
@@ -1395,13 +1395,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B72" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-05</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B73" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-05</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B74" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-05</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B75" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-05</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B76" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-05</v>
@@ -1465,13 +1465,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B77" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-05</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B78" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-05</v>
@@ -1493,13 +1493,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B79" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-05</v>
@@ -1507,21 +1507,259 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C80" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>רולי אזרחי - מרחוק להורדה</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C81" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>נרקיס בר-און - לו היית להורדה</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C82" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>משה דוויק - שיר תודה להורדה</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C83" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C84" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C86" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>אלי וינר - ניצחתי להורדה</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C87" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C88" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>זהבה - עדיין ילד להורדה</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C89" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>רותם גבאי - שדה חמניה להורדה</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C90" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C91" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C92" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C93" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C94" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C95" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C96" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B80" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C80" t="str">
+      <c r="B97" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C97" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D97" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D114"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,10 +418,10 @@
         <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B2" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-05</v>
@@ -432,10 +432,10 @@
         <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B3" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-05</v>
@@ -446,10 +446,10 @@
         <v>מאור יפרח - אמא</v>
       </c>
       <c r="B4" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-05</v>
@@ -460,10 +460,10 @@
         <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B5" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-05</v>
@@ -474,10 +474,10 @@
         <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B6" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-05</v>
@@ -488,10 +488,10 @@
         <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B7" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -502,10 +502,10 @@
         <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B8" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -516,10 +516,10 @@
         <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B9" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -530,10 +530,10 @@
         <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B10" t="str">
-        <v>eliad83</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -544,10 +544,10 @@
         <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B11" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -558,10 +558,10 @@
         <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B12" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -572,10 +572,10 @@
         <v>שייה - לפח</v>
       </c>
       <c r="B13" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -586,10 +586,10 @@
         <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B14" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -600,10 +600,10 @@
         <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B15" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -614,10 +614,10 @@
         <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B16" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -628,10 +628,10 @@
         <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B17" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -642,10 +642,10 @@
         <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B18" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -656,10 +656,10 @@
         <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B19" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -670,10 +670,10 @@
         <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B20" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -684,10 +684,10 @@
         <v>מאור יפרח - אמא</v>
       </c>
       <c r="B21" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -698,10 +698,10 @@
         <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B22" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -712,10 +712,10 @@
         <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B23" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -726,10 +726,10 @@
         <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B24" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -740,10 +740,10 @@
         <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B25" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -754,10 +754,10 @@
         <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B26" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -768,10 +768,10 @@
         <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B27" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -782,10 +782,10 @@
         <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B28" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B29" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B30" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B31" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B32" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B33" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B34" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B35" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B36" t="str">
         <v>0</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B37" t="str">
         <v>0</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B38" t="str">
         <v>0</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B39" t="str">
         <v>0</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>שייה - לפח</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B40" t="str">
         <v>0</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-05</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B41" t="str">
         <v>0</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-05</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B42" t="str">
         <v>0</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-05</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B43" t="str">
         <v>0</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-05</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B44" t="str">
         <v>0</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-05</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B45" t="str">
         <v>0</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-05</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>מני חן - תני סימן קטן לאהבה</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B46" t="str">
         <v>0</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-05</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ירין מסס - נדבר באהבה</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B47" t="str">
         <v>0</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-05</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>חן ביטון - התקרבתי</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B48" t="str">
         <v>0</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-05</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>החצר האחורית של ג'וני - הזקן</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B49" t="str">
         <v>0</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-05</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>אליה נרקיס - שכחת את הכל</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B50" t="str">
         <v>0</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-05</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>רולי אזרחי - מרחוק</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B51" t="str">
         <v>0</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-05</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>נרקיס בר-און - לו היית</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B52" t="str">
         <v>0</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-05</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>משה דוויק - שיר תודה</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B53" t="str">
         <v>0</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-05</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>משה גמל - עולה לי בדמעות</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B54" t="str">
         <v>0</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-05</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B55" t="str">
         <v>0</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-05</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>חביב חיים בן אריה - ותזרח</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B56" t="str">
         <v>0</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-05</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>אלי וינר - ניצחתי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B57" t="str">
         <v>0</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-05</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B58" t="str">
         <v>0</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-05</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B59" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-05</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B60" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-05</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B61" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-05</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B62" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-05</v>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B63" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-05</v>
@@ -1283,13 +1283,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B64" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-05</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B65" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-05</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B66" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-05</v>
@@ -1325,13 +1325,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B67" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-05</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B68" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-05</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B69" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-05</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B70" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-05</v>
@@ -1381,13 +1381,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B71" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-05</v>
@@ -1395,13 +1395,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B72" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-05</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B73" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-05</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B74" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-05</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B75" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-05</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B76" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-05</v>
@@ -1465,13 +1465,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B77" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-05</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B78" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-05</v>
@@ -1493,13 +1493,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B79" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-05</v>
@@ -1507,13 +1507,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B80" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-05</v>
@@ -1521,13 +1521,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B81" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-05</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B82" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-05</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B83" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-05</v>
@@ -1563,13 +1563,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B84" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-05</v>
@@ -1577,13 +1577,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B85" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-05</v>
@@ -1591,13 +1591,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B86" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-05</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B87" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-05</v>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B88" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-05</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B89" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-05</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B90" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-05</v>
@@ -1661,13 +1661,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B91" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-05</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B92" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-05</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B93" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-05</v>
@@ -1703,13 +1703,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B94" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-05</v>
@@ -1717,13 +1717,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B95" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-05</v>
@@ -1731,13 +1731,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B96" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-05</v>
@@ -1745,21 +1745,259 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C97" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>רולי אזרחי - מרחוק להורדה</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C98" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>נרקיס בר-און - לו היית להורדה</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C99" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>משה דוויק - שיר תודה להורדה</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C100" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C101" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C102" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C103" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>אלי וינר - ניצחתי להורדה</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C104" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C105" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>זהבה - עדיין ילד להורדה</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C106" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>רותם גבאי - שדה חמניה להורדה</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C107" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C108" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C109" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C110" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C111" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C112" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C113" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B97" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C97" t="str">
+      <c r="B114" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C114" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D97" t="str">
+      <c r="D114" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,83 +415,83 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>ישי סיידוף - בלילות</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>חנן ילד הפלא - ריקוד הנסיכה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>בנג׳מין בוזגלו - על הכל אני סולח</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>אופירה שופן - בא לי</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-05</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-05</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-05</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-05</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-05</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B19" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B20" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B21" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B22" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B23" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B24" t="str">
         <v>eliad83</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B25" t="str">
         <v>eliad83</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B26" t="str">
         <v>eliad83</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B27" t="str">
         <v>eliad83</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B28" t="str">
         <v>eliad83</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B29" t="str">
         <v>eliad83</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B30" t="str">
         <v>eliad83</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B31" t="str">
         <v>eliad83</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B32" t="str">
         <v>eliad83</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B33" t="str">
         <v>eliad83</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B34" t="str">
         <v>eliad83</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B35" t="str">
         <v>eliad83</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B36" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B37" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B38" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B39" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B40" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-05</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B41" t="str">
         <v>0</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-05</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B42" t="str">
         <v>0</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-05</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B43" t="str">
         <v>0</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-05</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B44" t="str">
         <v>0</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-05</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B45" t="str">
         <v>0</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-05</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B46" t="str">
         <v>0</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-05</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B47" t="str">
         <v>0</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-05</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B48" t="str">
         <v>0</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-05</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B49" t="str">
         <v>0</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-05</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B50" t="str">
         <v>0</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-05</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B51" t="str">
         <v>0</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-05</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B52" t="str">
         <v>0</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-05</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B53" t="str">
         <v>0</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-05</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B54" t="str">
         <v>0</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-05</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B55" t="str">
         <v>0</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-05</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B56" t="str">
         <v>0</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-05</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B57" t="str">
         <v>0</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-05</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B58" t="str">
         <v>0</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-05</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B59" t="str">
         <v>0</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-05</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B60" t="str">
         <v>0</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-05</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B61" t="str">
         <v>0</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-05</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B62" t="str">
         <v>0</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-05</v>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>מני חן - תני סימן קטן לאהבה</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B63" t="str">
         <v>0</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-05</v>
@@ -1283,13 +1283,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ירין מסס - נדבר באהבה</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B64" t="str">
         <v>0</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-05</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>חן ביטון - התקרבתי</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B65" t="str">
         <v>0</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-05</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>החצר האחורית של ג'וני - הזקן</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B66" t="str">
         <v>0</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-05</v>
@@ -1325,13 +1325,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>אליה נרקיס - שכחת את הכל</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B67" t="str">
         <v>0</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-05</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>רולי אזרחי - מרחוק</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B68" t="str">
         <v>0</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-05</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>נרקיס בר-און - לו היית</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B69" t="str">
         <v>0</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-05</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>משה דוויק - שיר תודה</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B70" t="str">
         <v>0</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-05</v>
@@ -1381,13 +1381,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>משה גמל - עולה לי בדמעות</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B71" t="str">
         <v>0</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-05</v>
@@ -1395,13 +1395,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B72" t="str">
         <v>0</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-05</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>חביב חיים בן אריה - ותזרח</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B73" t="str">
         <v>0</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-05</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>אלי וינר - ניצחתי</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B74" t="str">
         <v>0</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-05</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B75" t="str">
         <v>0</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-05</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B76" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-05</v>
@@ -1465,13 +1465,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B77" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-05</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B78" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-05</v>
@@ -1493,13 +1493,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B79" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-05</v>
@@ -1507,13 +1507,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B80" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-05</v>
@@ -1521,13 +1521,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B81" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-05</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B82" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-05</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B83" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-05</v>
@@ -1563,13 +1563,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B84" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-05</v>
@@ -1577,13 +1577,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B85" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-05</v>
@@ -1591,13 +1591,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B86" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-05</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B87" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-05</v>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B88" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-05</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B89" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-05</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B90" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-05</v>
@@ -1661,13 +1661,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B91" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-05</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B92" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-05</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B93" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-05</v>
@@ -1703,13 +1703,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B94" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-05</v>
@@ -1717,13 +1717,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B95" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-05</v>
@@ -1731,13 +1731,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B96" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-05</v>
@@ -1745,13 +1745,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B97" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-05</v>
@@ -1759,13 +1759,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B98" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-05</v>
@@ -1773,13 +1773,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B99" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-05</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B100" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-05</v>
@@ -1801,13 +1801,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B101" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-05</v>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
       </c>
       <c r="B102" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-05</v>
@@ -1829,13 +1829,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>רולי אזרחי - מרחוק להורדה</v>
       </c>
       <c r="B103" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-05</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>נרקיס בר-און - לו היית להורדה</v>
       </c>
       <c r="B104" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-05</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>משה דוויק - שיר תודה להורדה</v>
       </c>
       <c r="B105" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-05</v>
@@ -1871,13 +1871,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
       </c>
       <c r="B106" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-05</v>
@@ -1885,13 +1885,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
       </c>
       <c r="B107" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-05</v>
@@ -1899,13 +1899,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
       </c>
       <c r="B108" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-05</v>
@@ -1913,13 +1913,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>אלי וינר - ניצחתי להורדה</v>
       </c>
       <c r="B109" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-05</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
       </c>
       <c r="B110" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-05</v>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>זהבה - עדיין ילד להורדה</v>
       </c>
       <c r="B111" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-05</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>רותם גבאי - שדה חמניה להורדה</v>
       </c>
       <c r="B112" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-05</v>
@@ -1969,13 +1969,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
       </c>
       <c r="B113" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-05</v>
@@ -1983,21 +1983,91 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C114" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C115" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C116" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C117" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C118" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B114" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C114" t="str">
+      <c r="B119" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C119" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D119" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות</v>
+        <v>שיר לוי - רחוב ללא מוצא</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=e139ef8cdab17d61617599ad4952839b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-06</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישי סיידוף - בלילות</v>
+        <v>רועי אדרי - קומי לרקוד</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=e139ef8cdab17d61617599ad4952839b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-06</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>חנן ילד הפלא - ריקוד הנסיכה</v>
+        <v>רון פרץ - הוקוס פוקוס</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=e139ef8cdab17d61617599ad4952839b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-06</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בנג׳מין בוזגלו - על הכל אני סולח</v>
+        <v>קובי מירסקי - מחשבות</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=e139ef8cdab17d61617599ad4952839b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-06</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אופירה שופן - בא לי</v>
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=e139ef8cdab17d61617599ad4952839b</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-06</v>
@@ -485,83 +485,83 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>ישי סיידוף - בלילות</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>חנן ילד הפלא - ריקוד הנסיכה</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>בנג׳מין בוזגלו - על הכל אני סולח</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>אופירה שופן - בא לי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=daa14ee391fdb1945f1acec8393ef4a2</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-05</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-05</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-05</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-05</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-05</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-05</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-05</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-05</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-05</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-05</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-05</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-05</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-05</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-04</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-05</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B24" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-05</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B25" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-05</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B26" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-05</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B27" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-05</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B28" t="str">
-        <v>eliad83</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=f9024d41c3eb461f8950658a7906fdba</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-05</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B29" t="str">
         <v>eliad83</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-05</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B30" t="str">
         <v>eliad83</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-05</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B31" t="str">
         <v>eliad83</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-05</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B32" t="str">
         <v>eliad83</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-05</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B33" t="str">
         <v>eliad83</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-05</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B34" t="str">
         <v>eliad83</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-05</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B35" t="str">
         <v>eliad83</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-05</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B36" t="str">
         <v>eliad83</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-05</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B37" t="str">
         <v>eliad83</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-05</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B38" t="str">
         <v>eliad83</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-05</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B39" t="str">
         <v>eliad83</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-05</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B40" t="str">
         <v>eliad83</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-05</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B41" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-05</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B42" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-05</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B43" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-05</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B44" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-05</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B45" t="str">
-        <v>0</v>
+        <v>eliad83</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=abdf171a50addfad2126b5bae37c2475</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-05</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B46" t="str">
         <v>0</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-05</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B47" t="str">
         <v>0</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-05</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B48" t="str">
         <v>0</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-05</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B49" t="str">
         <v>0</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-05</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B50" t="str">
         <v>0</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-05</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>שחר חדד - אחד בשביל אחד</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B51" t="str">
         <v>0</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-05</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>נלה' - כמו וויסקי</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B52" t="str">
         <v>0</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-05</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>מאור יפרח - אמא</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B53" t="str">
         <v>0</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-05</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ישראל מועלמי - בית משוגעים</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B54" t="str">
         <v>0</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-05</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B55" t="str">
         <v>0</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=9c4e1ed47494f51f496cde19d63a7ea2</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-05</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>התאומים - Ah Yar Cover</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B56" t="str">
         <v>0</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-05</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B57" t="str">
         <v>0</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-05</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>אנג'ל אלישע - שמחתית</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B58" t="str">
         <v>0</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-05</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B59" t="str">
         <v>0</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-05</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B60" t="str">
         <v>0</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-05</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>שירז אברהם - היית לי עיניים</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B61" t="str">
         <v>0</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-05</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>שייה - לפח</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B62" t="str">
         <v>0</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-05</v>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>רותם כהן - לשרוף</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B63" t="str">
         <v>0</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-05</v>
@@ -1283,13 +1283,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>קלימה - תודה בורא עולם</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B64" t="str">
         <v>0</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-05</v>
@@ -1297,13 +1297,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>דוד ברג - אזמרה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים</v>
       </c>
       <c r="B65" t="str">
         <v>0</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-05</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>אבירם פרחן - בגדו בי</v>
+        <v>שירז אברהם - היית לי עיניים</v>
       </c>
       <c r="B66" t="str">
         <v>0</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-05</v>
@@ -1325,13 +1325,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ניסן כהן - מה שלא תרצי</v>
+        <v>שייה - לפח</v>
       </c>
       <c r="B67" t="str">
         <v>0</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-05</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>מני חן - תני סימן קטן לאהבה</v>
+        <v>רותם כהן - לשרוף</v>
       </c>
       <c r="B68" t="str">
         <v>0</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-05</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ירין מסס - נדבר באהבה</v>
+        <v>קלימה - תודה בורא עולם</v>
       </c>
       <c r="B69" t="str">
         <v>0</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-05</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>חן ביטון - התקרבתי</v>
+        <v>דוד ברג - אזמרה</v>
       </c>
       <c r="B70" t="str">
         <v>0</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-05</v>
@@ -1381,13 +1381,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>החצר האחורית של ג'וני - הזקן</v>
+        <v>אבירם פרחן - בגדו בי</v>
       </c>
       <c r="B71" t="str">
         <v>0</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-05</v>
@@ -1395,13 +1395,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>אליה נרקיס - שכחת את הכל</v>
+        <v>ניסן כהן - מה שלא תרצי</v>
       </c>
       <c r="B72" t="str">
         <v>0</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-05</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>רולי אזרחי - מרחוק</v>
+        <v>מני חן - תני סימן קטן לאהבה</v>
       </c>
       <c r="B73" t="str">
         <v>0</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-05</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>נרקיס בר-און - לו היית</v>
+        <v>ירין מסס - נדבר באהבה</v>
       </c>
       <c r="B74" t="str">
         <v>0</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-05</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>משה דוויק - שיר תודה</v>
+        <v>חן ביטון - התקרבתי</v>
       </c>
       <c r="B75" t="str">
         <v>0</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-05</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>משה גמל - עולה לי בדמעות</v>
+        <v>החצר האחורית של ג'וני - הזקן</v>
       </c>
       <c r="B76" t="str">
         <v>0</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-05</v>
@@ -1465,13 +1465,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן</v>
+        <v>אליה נרקיס - שכחת את הכל</v>
       </c>
       <c r="B77" t="str">
         <v>0</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-05</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>חביב חיים בן אריה - ותזרח</v>
+        <v>רולי אזרחי - מרחוק</v>
       </c>
       <c r="B78" t="str">
         <v>0</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-05</v>
@@ -1493,13 +1493,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>אלי וינר - ניצחתי</v>
+        <v>נרקיס בר-און - לו היית</v>
       </c>
       <c r="B79" t="str">
         <v>0</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-05</v>
@@ -1507,13 +1507,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
+        <v>משה דוויק - שיר תודה</v>
       </c>
       <c r="B80" t="str">
         <v>0</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-05</v>
@@ -1521,13 +1521,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>משה גמל - עולה לי בדמעות</v>
       </c>
       <c r="B81" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-05</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן</v>
       </c>
       <c r="B82" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-05</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח</v>
       </c>
       <c r="B83" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-05</v>
@@ -1563,13 +1563,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>אלי וינר - ניצחתי</v>
       </c>
       <c r="B84" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-05</v>
@@ -1577,13 +1577,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך</v>
       </c>
       <c r="B85" t="str">
-        <v>2000-01-01</v>
+        <v>0</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=5069609bc230649a60ba5ab33793c224</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-05</v>
@@ -1591,13 +1591,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
       </c>
       <c r="B86" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-05</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>נלה' - כמו וויסקי להורדה</v>
       </c>
       <c r="B87" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-05</v>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>מאור יפרח - אמא להורדה</v>
       </c>
       <c r="B88" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-05</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
       </c>
       <c r="B89" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=0da22781236179f62402c6543c36a23c</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-05</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
       </c>
       <c r="B90" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-05</v>
@@ -1661,13 +1661,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>שירז אברהם - היית לי עיניים להורדה</v>
+        <v>התאומים - Ah Yar Cover להורדה</v>
       </c>
       <c r="B91" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-05</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>שייה - לפח להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
       </c>
       <c r="B92" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-05</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>רותם כהן - לשרוף להורדה</v>
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
       </c>
       <c r="B93" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-05</v>
@@ -1703,13 +1703,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>קלימה - תודה בורא עולם להורדה</v>
+        <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
       <c r="B94" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=9fd2e6b655db2612e5fa177d3bb9c092</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-05</v>
@@ -1717,13 +1717,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>דוד ברג - אזמרה להורדה</v>
+        <v>שריי אדר &amp; אודימן - הבל הבלים להורדה</v>
       </c>
       <c r="B95" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409064&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-05</v>
@@ -1731,13 +1731,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>אבירם פרחן - בגדו בי להורדה</v>
+        <v>שירז אברהם - היית לי עיניים להורדה</v>
       </c>
       <c r="B96" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409063&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-05</v>
@@ -1745,13 +1745,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ניסן כהן - מה שלא תרצי להורדה</v>
+        <v>שייה - לפח להורדה</v>
       </c>
       <c r="B97" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409062&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-05</v>
@@ -1759,13 +1759,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
+        <v>רותם כהן - לשרוף להורדה</v>
       </c>
       <c r="B98" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409061&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-05</v>
@@ -1773,13 +1773,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ירין מסס - נדבר באהבה להורדה</v>
+        <v>קלימה - תודה בורא עולם להורדה</v>
       </c>
       <c r="B99" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409060&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-05</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>חן ביטון - התקרבתי להורדה</v>
+        <v>דוד ברג - אזמרה להורדה</v>
       </c>
       <c r="B100" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409059&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-05</v>
@@ -1801,13 +1801,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
+        <v>אבירם פרחן - בגדו בי להורדה</v>
       </c>
       <c r="B101" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409058&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-05</v>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>אליה נרקיס - שכחת את הכל להורדה</v>
+        <v>ניסן כהן - מה שלא תרצי להורדה</v>
       </c>
       <c r="B102" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409057&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-05</v>
@@ -1829,13 +1829,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>רולי אזרחי - מרחוק להורדה</v>
+        <v>מני חן - תני סימן קטן לאהבה להורדה</v>
       </c>
       <c r="B103" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409056&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-05</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>נרקיס בר-און - לו היית להורדה</v>
+        <v>ירין מסס - נדבר באהבה להורדה</v>
       </c>
       <c r="B104" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409055&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-05</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>משה דוויק - שיר תודה להורדה</v>
+        <v>חן ביטון - התקרבתי להורדה</v>
       </c>
       <c r="B105" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409054&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-05</v>
@@ -1871,13 +1871,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>משה גמל - עולה לי בדמעות להורדה</v>
+        <v>החצר האחורית של ג'וני - הזקן להורדה</v>
       </c>
       <c r="B106" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409053&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-05</v>
@@ -1885,13 +1885,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
+        <v>אליה נרקיס - שכחת את הכל להורדה</v>
       </c>
       <c r="B107" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409052&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-05</v>
@@ -1899,13 +1899,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>חביב חיים בן אריה - ותזרח להורדה</v>
+        <v>רולי אזרחי - מרחוק להורדה</v>
       </c>
       <c r="B108" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409042&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-05</v>
@@ -1913,13 +1913,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>אלי וינר - ניצחתי להורדה</v>
+        <v>נרקיס בר-און - לו היית להורדה</v>
       </c>
       <c r="B109" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409041&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-05</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
+        <v>משה דוויק - שיר תודה להורדה</v>
       </c>
       <c r="B110" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409040&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-05</v>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>זהבה - עדיין ילד להורדה</v>
+        <v>משה גמל - עולה לי בדמעות להורדה</v>
       </c>
       <c r="B111" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409039&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-05</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>רותם גבאי - שדה חמניה להורדה</v>
+        <v>מיכאל סימן טוב - האחת מכולן להורדה</v>
       </c>
       <c r="B112" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409038&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-05</v>
@@ -1969,13 +1969,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
+        <v>חביב חיים בן אריה - ותזרח להורדה</v>
       </c>
       <c r="B113" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409037&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-05</v>
@@ -1983,13 +1983,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+        <v>אלי וינר - ניצחתי להורדה</v>
       </c>
       <c r="B114" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409036&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-05</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את מוישי רוט - ממקומך להורדה</v>
       </c>
       <c r="B115" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409035&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-05</v>
@@ -2011,13 +2011,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>טל ועקנין - השבעתי להורדה</v>
+        <v>זהבה - עדיין ילד להורדה</v>
       </c>
       <c r="B116" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409025&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-05</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+        <v>רותם גבאי - שדה חמניה להורדה</v>
       </c>
       <c r="B117" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409024&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-05</v>
@@ -2039,13 +2039,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>ניב אבוטבול - אהבה מטורפת כמוך - 007 להורדה</v>
       </c>
       <c r="B118" t="str">
         <v>2000-01-01</v>
       </c>
       <c r="C118" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409023&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-05</v>
@@ -2053,21 +2053,91 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
+        <v>מעיין וגן - תלך כמו גבר להורדה</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C119" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409022&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>מושיקו מזרחי - תושיט לי ידיים להורדה</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C120" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409021&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>טל ועקנין - השבעתי להורדה</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C121" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409020&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>זיו גבאי - אערוך מהלל ניבי להורדה</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C122" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409019&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C123" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
         <v>אלמוג טויטו - אוהב מכל הלב להורדה</v>
       </c>
-      <c r="B119" t="str">
-        <v>2000-01-01</v>
-      </c>
-      <c r="C119" t="str">
+      <c r="B124" t="str">
+        <v>2000-01-01</v>
+      </c>
+      <c r="C124" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409017&amp;sid=2e878ac5f264f063c3180b44849b02fa</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D124" t="str">
         <v>2026-01-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי דאבוש - המילה הנכונה להורדה</v>
+        <v>שלומי דאבוש - המילה הנכונה ל</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-07</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן להורדה</v>
+        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן ל</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-07</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מתנאל אסייג - בין הפטיש לסדן להורדה</v>
+        <v>מתנאל אסייג - בין הפטיש לסדן ל</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-07</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מור זיתוני - אני ואני להורדה</v>
+        <v>מור זיתוני - אני ואני ל</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-07</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור נחום - אחרי הכל להורדה</v>
+        <v>לידור נחום - אחרי הכל ל</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-07</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור מיארה - שרפת אותי בחוץ להורדה</v>
+        <v>ליאור מיארה - שרפת אותי בחוץ ל</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-07</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>זוהר אשירוב - ילדה רעה להורדה</v>
+        <v>זוהר אשירוב - ילדה רעה ל</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-07</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלינור חלילוב - רצה אחריך להורדה</v>
+        <v>אלינור חלילוב - רצה אחריך ל</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-07</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אברהם דהאן - כמה לילות להורדה</v>
+        <v>אברהם דהאן - כמה לילות ל</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-07</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אביחי מלכה - זוכר אותך להורדה</v>
+        <v>אביחי מלכה - זוכר אותך ל</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-07</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>היוצרים - יאמה ל</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-07</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שיר לוי - רחוב ללא מוצא להורדה</v>
+        <v>שיר לוי - רחוב ללא מוצא ל</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-07</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>רועי אדרי - קומי לרקוד להורדה</v>
+        <v>רועי אדרי - קומי לרקוד ל</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-07</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>רון פרץ - הוקוס פוקוס להורדה</v>
+        <v>רון פרץ - הוקוס פוקוס ל</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-07</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>קובי מירסקי - מחשבות להורדה</v>
+        <v>קובי מירסקי - מחשבות ל</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-07</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ להורדה</v>
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ ל</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-07</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות להורדה</v>
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות ל</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-07</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ישי סיידוף - בלילות להורדה</v>
+        <v>ישי סיידוף - בלילות ל</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-07</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>חנן ילד הפלא - ריקוד הנסיכה להורדה</v>
+        <v>חנן ילד הפלא - ריקוד הנסיכה ל</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-07</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>בנג׳מין בוזגלו - על הכל אני סולח להורדה</v>
+        <v>בנג׳מין בוזגלו - על הכל אני סולח ל</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-07</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אופירה שופן - בא לי להורדה</v>
+        <v>אופירה שופן - בא לי ל</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-07</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד ל</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-07</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>נלה' - כמו וויסקי ל</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-07</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>מאור יפרח - אמא ל</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-07</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים ל</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-07</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי ל</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-07</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>התאומים - Ah Yar Cover ל</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-07</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע ל</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-07</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>אנג'ל אלישע - שמחתית ל</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-07</v>
@@ -821,21 +821,441 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>אחיה אדרי - כל הטוב בשבילי ל</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=179fa96897225611658d546c3401083b</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>שלומי דאבוש - המילה הנכונה להורדה</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C32" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן להורדה</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C33" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>מתנאל אסייג - בין הפטיש לסדן להורדה</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C34" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>מור זיתוני - אני ואני להורדה</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C35" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>לידור נחום - אחרי הכל להורדה</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C36" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>ליאור מיארה - שרפת אותי בחוץ להורדה</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C37" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>זוהר אשירוב - ילדה רעה להורדה</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C38" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>אלינור חלילוב - רצה אחריך להורדה</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C39" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>אברהם דהאן - כמה לילות להורדה</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C40" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>אביחי מלכה - זוכר אותך להורדה</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C41" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C42" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>שיר לוי - רחוב ללא מוצא להורדה</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C43" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>רועי אדרי - קומי לרקוד להורדה</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C44" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>רון פרץ - הוקוס פוקוס להורדה</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C45" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>קובי מירסקי - מחשבות להורדה</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C46" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ להורדה</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C47" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות להורדה</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C48" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>ישי סיידוף - בלילות להורדה</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C49" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>חנן ילד הפלא - ריקוד הנסיכה להורדה</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C50" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>בנג׳מין בוזגלו - על הכל אני סולח להורדה</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C51" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>אופירה שופן - בא לי להורדה</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C52" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C53" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>נלה' - כמו וויסקי להורדה</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C54" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>מאור יפרח - אמא להורדה</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C55" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C56" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C57" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>התאומים - Ah Yar Cover להורדה</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C58" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C59" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C60" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
         <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
-      <c r="B31" t="str">
-        <v>2026-01-05</v>
-      </c>
-      <c r="C31" t="str">
+      <c r="B61" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C61" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D61" t="str">
         <v>2026-01-07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/sites/mizrahit/titles.xlsx
+++ b/data/sites/mizrahit/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,13 +415,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי דאבוש - המילה הנכונה ל</v>
+        <v>שלומי דאבוש - המילה הנכונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-07</v>
@@ -429,13 +429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן ל</v>
+        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-07</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מתנאל אסייג - בין הפטיש לסדן ל</v>
+        <v>מתנאל אסייג - בין הפטיש לסדן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-07</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מור זיתוני - אני ואני ל</v>
+        <v>מור זיתוני - אני ואני</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-07</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור נחום - אחרי הכל ל</v>
+        <v>לידור נחום - אחרי הכל</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-07</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור מיארה - שרפת אותי בחוץ ל</v>
+        <v>ליאור מיארה - שרפת אותי בחוץ</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-07</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>זוהר אשירוב - ילדה רעה ל</v>
+        <v>זוהר אשירוב - ילדה רעה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-07</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלינור חלילוב - רצה אחריך ל</v>
+        <v>אלינור חלילוב - רצה אחריך</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-07</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אברהם דהאן - כמה לילות ל</v>
+        <v>אברהם דהאן - כמה לילות</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-07</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אביחי מלכה - זוכר אותך ל</v>
+        <v>אביחי מלכה - זוכר אותך</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-07</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>היוצרים - יאמה ל</v>
+        <v>היוצרים - יאמה</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-07</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שיר לוי - רחוב ללא מוצא ל</v>
+        <v>שיר לוי - רחוב ללא מוצא</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-07</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>רועי אדרי - קומי לרקוד ל</v>
+        <v>רועי אדרי - קומי לרקוד</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-07</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>רון פרץ - הוקוס פוקוס ל</v>
+        <v>רון פרץ - הוקוס פוקוס</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-07</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>קובי מירסקי - מחשבות ל</v>
+        <v>קובי מירסקי - מחשבות</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-07</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ ל</v>
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-07</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות ל</v>
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-07</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ישי סיידוף - בלילות ל</v>
+        <v>ישי סיידוף - בלילות</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-07</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>חנן ילד הפלא - ריקוד הנסיכה ל</v>
+        <v>חנן ילד הפלא - ריקוד הנסיכה</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-07</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>בנג׳מין בוזגלו - על הכל אני סולח ל</v>
+        <v>בנג׳מין בוזגלו - על הכל אני סולח</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-07</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אופירה שופן - בא לי ל</v>
+        <v>אופירה שופן - בא לי</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-07</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>שחר חדד - אחד בשביל אחד ל</v>
+        <v>שחר חדד - אחד בשביל אחד</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-07</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>נלה' - כמו וויסקי ל</v>
+        <v>נלה' - כמו וויסקי</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-07</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>מאור יפרח - אמא ל</v>
+        <v>מאור יפרח - אמא</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-07</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ישראל מועלמי - בית משוגעים ל</v>
+        <v>ישראל מועלמי - בית משוגעים</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-07</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי ל</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-07</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>התאומים - Ah Yar Cover ל</v>
+        <v>התאומים - Ah Yar Cover</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-07</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע ל</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-07</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אנג'ל אלישע - שמחתית ל</v>
+        <v>אנג'ל אלישע - שמחתית</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-07</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אחיה אדרי - כל הטוב בשבילי ל</v>
+        <v>אחיה אדרי - כל הטוב בשבילי</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=179fa96897225611658d546c3401083b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=c78410fae149295fa52f3516b24d3ca9</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-07</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>שלומי דאבוש - המילה הנכונה להורדה</v>
+        <v>שלומי דאבוש - המילה הנכונה ל</v>
       </c>
       <c r="B32" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-07</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן להורדה</v>
+        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן ל</v>
       </c>
       <c r="B33" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-07</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>מתנאל אסייג - בין הפטיש לסדן להורדה</v>
+        <v>מתנאל אסייג - בין הפטיש לסדן ל</v>
       </c>
       <c r="B34" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-07</v>
@@ -877,13 +877,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>מור זיתוני - אני ואני להורדה</v>
+        <v>מור זיתוני - אני ואני ל</v>
       </c>
       <c r="B35" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-07</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>לידור נחום - אחרי הכל להורדה</v>
+        <v>לידור נחום - אחרי הכל ל</v>
       </c>
       <c r="B36" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-07</v>
@@ -905,13 +905,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ליאור מיארה - שרפת אותי בחוץ להורדה</v>
+        <v>ליאור מיארה - שרפת אותי בחוץ ל</v>
       </c>
       <c r="B37" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-07</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>זוהר אשירוב - ילדה רעה להורדה</v>
+        <v>זוהר אשירוב - ילדה רעה ל</v>
       </c>
       <c r="B38" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-07</v>
@@ -933,13 +933,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>אלינור חלילוב - רצה אחריך להורדה</v>
+        <v>אלינור חלילוב - רצה אחריך ל</v>
       </c>
       <c r="B39" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-07</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>אברהם דהאן - כמה לילות להורדה</v>
+        <v>אברהם דהאן - כמה לילות ל</v>
       </c>
       <c r="B40" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-07</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>אביחי מלכה - זוכר אותך להורדה</v>
+        <v>אביחי מלכה - זוכר אותך ל</v>
       </c>
       <c r="B41" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-07</v>
@@ -975,13 +975,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>היוצרים - יאמה להורדה</v>
+        <v>היוצרים - יאמה ל</v>
       </c>
       <c r="B42" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-07</v>
@@ -989,13 +989,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>שיר לוי - רחוב ללא מוצא להורדה</v>
+        <v>שיר לוי - רחוב ללא מוצא ל</v>
       </c>
       <c r="B43" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-07</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>רועי אדרי - קומי לרקוד להורדה</v>
+        <v>רועי אדרי - קומי לרקוד ל</v>
       </c>
       <c r="B44" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-07</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>רון פרץ - הוקוס פוקוס להורדה</v>
+        <v>רון פרץ - הוקוס פוקוס ל</v>
       </c>
       <c r="B45" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-07</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>קובי מירסקי - מחשבות להורדה</v>
+        <v>קובי מירסקי - מחשבות ל</v>
       </c>
       <c r="B46" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-07</v>
@@ -1045,13 +1045,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ להורדה</v>
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ ל</v>
       </c>
       <c r="B47" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-07</v>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות להורדה</v>
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות ל</v>
       </c>
       <c r="B48" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-07</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ישי סיידוף - בלילות להורדה</v>
+        <v>ישי סיידוף - בלילות ל</v>
       </c>
       <c r="B49" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-07</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>חנן ילד הפלא - ריקוד הנסיכה להורדה</v>
+        <v>חנן ילד הפלא - ריקוד הנסיכה ל</v>
       </c>
       <c r="B50" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-07</v>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>בנג׳מין בוזגלו - על הכל אני סולח להורדה</v>
+        <v>בנג׳מין בוזגלו - על הכל אני סולח ל</v>
       </c>
       <c r="B51" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-07</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>אופירה שופן - בא לי להורדה</v>
+        <v>אופירה שופן - בא לי ל</v>
       </c>
       <c r="B52" t="str">
         <v>2026-01-06</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-07</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+        <v>שחר חדד - אחד בשביל אחד ל</v>
       </c>
       <c r="B53" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-07</v>
@@ -1143,13 +1143,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>נלה' - כמו וויסקי להורדה</v>
+        <v>נלה' - כמו וויסקי ל</v>
       </c>
       <c r="B54" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-07</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>מאור יפרח - אמא להורדה</v>
+        <v>מאור יפרח - אמא ל</v>
       </c>
       <c r="B55" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-07</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+        <v>ישראל מועלמי - בית משוגעים ל</v>
       </c>
       <c r="B56" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-07</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי ל</v>
       </c>
       <c r="B57" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-07</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>התאומים - Ah Yar Cover להורדה</v>
+        <v>התאומים - Ah Yar Cover ל</v>
       </c>
       <c r="B58" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-07</v>
@@ -1213,13 +1213,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+        <v>דוד וייה - אל תחזרי בעוד שבוע ל</v>
       </c>
       <c r="B59" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-07</v>
@@ -1227,13 +1227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>אנג'ל אלישע - שמחתית להורדה</v>
+        <v>אנג'ל אלישע - שמחתית ל</v>
       </c>
       <c r="B60" t="str">
         <v>2026-01-05</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=179fa96897225611658d546c3401083b</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-07</v>
@@ -1241,21 +1241,441 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>אחיה אדרי - כל הטוב בשבילי ל</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C61" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=179fa96897225611658d546c3401083b</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>שלומי דאבוש - המילה הנכונה להורדה</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C62" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409094&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>עומרי פילס &amp; טלי בינר - הדשא של השכן להורדה</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C63" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409093&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>מתנאל אסייג - בין הפטיש לסדן להורדה</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C64" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409092&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>מור זיתוני - אני ואני להורדה</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C65" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409091&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>לידור נחום - אחרי הכל להורדה</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C66" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409090&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>ליאור מיארה - שרפת אותי בחוץ להורדה</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C67" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409089&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>זוהר אשירוב - ילדה רעה להורדה</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C68" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409088&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>אלינור חלילוב - רצה אחריך להורדה</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C69" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409087&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>אברהם דהאן - כמה לילות להורדה</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C70" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409086&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>אביחי מלכה - זוכר אותך להורדה</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C71" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409085&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>היוצרים - יאמה להורדה</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C72" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409018&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>שיר לוי - רחוב ללא מוצא להורדה</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C73" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409084&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>רועי אדרי - קומי לרקוד להורדה</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C74" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409083&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>רון פרץ - הוקוס פוקוס להורדה</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C75" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409082&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>קובי מירסקי - מחשבות להורדה</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C76" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409081&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>עילי צ׳פמן &amp; נתנאל דהאן - גאדאמ להורדה</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C77" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409080&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>עדן בן זקן &amp; נדב חנציס - אלף חרבות להורדה</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C78" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409079&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>ישי סיידוף - בלילות להורדה</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C79" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409078&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>חנן ילד הפלא - ריקוד הנסיכה להורדה</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C80" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409077&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>בנג׳מין בוזגלו - על הכל אני סולח להורדה</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C81" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409076&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אופירה שופן - בא לי להורדה</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="C82" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409075&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>שחר חדד - אחד בשביל אחד להורדה</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C83" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409074&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>נלה' - כמו וויסקי להורדה</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C84" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409073&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>מאור יפרח - אמא להורדה</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C85" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409072&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>ישראל מועלמי - בית משוגעים להורדה</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C86" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409070&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>דודא &amp; ליעד מאיר - תבדוק׳תי להורדה</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C87" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409069&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>התאומים - Ah Yar Cover להורדה</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C88" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409068&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>דוד וייה - אל תחזרי בעוד שבוע להורדה</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C89" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409067&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>אנג'ל אלישע - שמחתית להורדה</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C90" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409066&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-07</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
         <v>אחיה אדרי - כל הטוב בשבילי להורדה</v>
       </c>
-      <c r="B61" t="str">
-        <v>2026-01-05</v>
-      </c>
-      <c r="C61" t="str">
+      <c r="B91" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="C91" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409065&amp;sid=453c4d9161a8ff76ca951751306ce899</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D91" t="str">
         <v>2026-01-07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D91"/>
   </ignoredErrors>
 </worksheet>
 </file>